--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2015_T4_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2015_T4_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>92</t>
+    <t>88</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>2.349</t>
-  </si>
-  <si>
-    <t>(1.312)</t>
-  </si>
-  <si>
-    <t>5.293</t>
-  </si>
-  <si>
-    <t>(0.705)</t>
-  </si>
-  <si>
-    <t>19.810</t>
-  </si>
-  <si>
-    <t>(5.322)</t>
-  </si>
-  <si>
-    <t>25.197</t>
-  </si>
-  <si>
-    <t>(6.420)</t>
-  </si>
-  <si>
-    <t>1.444</t>
-  </si>
-  <si>
-    <t>(0.274)</t>
-  </si>
-  <si>
-    <t>7.457</t>
-  </si>
-  <si>
-    <t>(0.864)</t>
-  </si>
-  <si>
-    <t>1.017</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
+    <t>0.919</t>
+  </si>
+  <si>
+    <t>(0.123)</t>
+  </si>
+  <si>
+    <t>5.511</t>
+  </si>
+  <si>
+    <t>(0.728)</t>
+  </si>
+  <si>
+    <t>12.529</t>
+  </si>
+  <si>
+    <t>(1.739)</t>
+  </si>
+  <si>
+    <t>16.573</t>
+  </si>
+  <si>
+    <t>(2.033)</t>
+  </si>
+  <si>
+    <t>1.509</t>
+  </si>
+  <si>
+    <t>(0.284)</t>
+  </si>
+  <si>
+    <t>7.795</t>
+  </si>
+  <si>
+    <t>(0.886)</t>
+  </si>
+  <si>
+    <t>1.037</t>
+  </si>
+  <si>
+    <t>(0.139)</t>
   </si>
   <si>
     <t>0.578</t>
   </si>
   <si>
-    <t>(0.111)</t>
-  </si>
-  <si>
-    <t>28.814</t>
-  </si>
-  <si>
-    <t>(5.740)</t>
-  </si>
-  <si>
-    <t>22.499</t>
-  </si>
-  <si>
-    <t>(7.531)</t>
+    <t>(0.114)</t>
+  </si>
+  <si>
+    <t>21.564</t>
+  </si>
+  <si>
+    <t>(2.371)</t>
+  </si>
+  <si>
+    <t>11.942</t>
+  </si>
+  <si>
+    <t>(1.753)</t>
   </si>
   <si>
     <t>22</t>
@@ -198,7 +198,7 @@
     <t>(6.368)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-1.034</t>
-  </si>
-  <si>
-    <t>0.116</t>
-  </si>
-  <si>
-    <t>15.532</t>
-  </si>
-  <si>
-    <t>16.261</t>
-  </si>
-  <si>
-    <t>0.282</t>
-  </si>
-  <si>
-    <t>-0.866</t>
-  </si>
-  <si>
-    <t>1.399***</t>
+    <t>0.395</t>
+  </si>
+  <si>
+    <t>-0.102</t>
+  </si>
+  <si>
+    <t>22.813***</t>
+  </si>
+  <si>
+    <t>24.885***</t>
+  </si>
+  <si>
+    <t>0.216</t>
+  </si>
+  <si>
+    <t>-1.205</t>
+  </si>
+  <si>
+    <t>1.379***</t>
   </si>
   <si>
     <t>0.082</t>
   </si>
   <si>
-    <t>25.183*</t>
-  </si>
-  <si>
-    <t>7.242</t>
+    <t>32.434***</t>
+  </si>
+  <si>
+    <t>17.799***</t>
   </si>
 </sst>
 </file>
